--- a/MinMax/scripts/comparison/accuracy_comparison_table_118_1000_True.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_118_1000_True.xlsx
@@ -34,85 +34,85 @@
     <t>Ibr_from_r_tot</t>
   </si>
   <si>
+    <t>pd_tot</t>
+  </si>
+  <si>
+    <t>slack_tot</t>
+  </si>
+  <si>
+    <t>pinj_tot</t>
+  </si>
+  <si>
+    <t>qinj_tot</t>
+  </si>
+  <si>
+    <t>vi_tot</t>
+  </si>
+  <si>
+    <t>Iinj_r_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_r_tot</t>
+  </si>
+  <si>
+    <t>solve_time</t>
+  </si>
+  <si>
+    <t>cost_tot</t>
+  </si>
+  <si>
+    <t>vr_tot</t>
+  </si>
+  <si>
+    <t>Ibr_from_i_tot</t>
+  </si>
+  <si>
+    <t>qg_tot</t>
+  </si>
+  <si>
+    <t>vm_tot</t>
+  </si>
+  <si>
+    <t>pg_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_i_tot</t>
+  </si>
+  <si>
+    <t>qd_tot</t>
+  </si>
+  <si>
     <t>Iinj_i_tot</t>
   </si>
   <si>
-    <t>Ibr_from_i_tot</t>
-  </si>
-  <si>
-    <t>pinj_tot</t>
-  </si>
-  <si>
-    <t>solve_time</t>
-  </si>
-  <si>
-    <t>pd_tot</t>
-  </si>
-  <si>
-    <t>Iinj_r_tot</t>
-  </si>
-  <si>
-    <t>qd_tot</t>
-  </si>
-  <si>
-    <t>vi_tot</t>
-  </si>
-  <si>
-    <t>qg_tot</t>
-  </si>
-  <si>
-    <t>vm_tot</t>
-  </si>
-  <si>
-    <t>vr_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_i_tot</t>
-  </si>
-  <si>
-    <t>qinj_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_r_tot</t>
-  </si>
-  <si>
-    <t>pg_tot</t>
-  </si>
-  <si>
-    <t>slack_tot</t>
-  </si>
-  <si>
-    <t>cost_tot</t>
-  </si>
-  <si>
-    <t>3.72s (18.06 s)</t>
-  </si>
-  <si>
     <t>2.45 (1.97)</t>
   </si>
   <si>
+    <t>4.77s (20.34 s)</t>
+  </si>
+  <si>
     <t>89911.75 (70058.73 &gt; 28.66%)</t>
   </si>
   <si>
-    <t>3.42s (18.06 s)</t>
-  </si>
-  <si>
     <t>1.85 (1.97)</t>
   </si>
   <si>
+    <t>3.71s (20.34 s)</t>
+  </si>
+  <si>
     <t>73759.09 (70058.73 &gt; 5.07%)</t>
   </si>
   <si>
-    <t>14.62s (18.06 s)</t>
-  </si>
-  <si>
     <t>1.97 (1.97)</t>
   </si>
   <si>
+    <t>20.45s (20.34 s)</t>
+  </si>
+  <si>
     <t>70057.65 (70058.73 &gt; 0.01%)</t>
   </si>
   <si>
-    <t>9.01s (18.06 s)</t>
+    <t>11.78s (20.34 s)</t>
   </si>
 </sst>
 </file>
@@ -512,33 +512,33 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0.06551679968833923</v>
+        <v>1.415648811724072E-16</v>
       </c>
       <c r="C3">
-        <v>0.03050441108644009</v>
+        <v>1.415648811724072E-16</v>
       </c>
       <c r="D3">
-        <v>0.006228530779480934</v>
+        <v>1.415648811724072E-16</v>
       </c>
       <c r="E3">
-        <v>0.006228530779480934</v>
+        <v>1.415648811724072E-16</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4">
-        <v>0.01823791675269604</v>
-      </c>
-      <c r="C4">
-        <v>0.01264662388712168</v>
-      </c>
-      <c r="D4">
-        <v>0.001363039249554276</v>
-      </c>
-      <c r="E4">
-        <v>0.001363039249554276</v>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -562,17 +562,17 @@
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>32</v>
+      <c r="B6">
+        <v>0.02194621413946152</v>
+      </c>
+      <c r="C6">
+        <v>0.03095167316496372</v>
+      </c>
+      <c r="D6">
+        <v>0.00682216277346015</v>
+      </c>
+      <c r="E6">
+        <v>0.00682216277346015</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -580,16 +580,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>1.415648811724072E-16</v>
+        <v>0.01917550526559353</v>
       </c>
       <c r="C7">
-        <v>1.415648811724072E-16</v>
+        <v>0.0004515898181125522</v>
       </c>
       <c r="D7">
-        <v>1.415648811724072E-16</v>
+        <v>2.304499730598764E-06</v>
       </c>
       <c r="E7">
-        <v>1.415648811724072E-16</v>
+        <v>2.304499730598764E-06</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -614,50 +614,50 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>2.120720691379777E-17</v>
+        <v>0.2837054133415222</v>
       </c>
       <c r="C9">
-        <v>2.120720691379777E-17</v>
+        <v>0.006657296791672707</v>
       </c>
       <c r="D9">
-        <v>2.120720691379777E-17</v>
+        <v>2.60684646491427E-05</v>
       </c>
       <c r="E9">
-        <v>2.120720691379777E-17</v>
+        <v>2.60684646491427E-05</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B10">
-        <v>0.01917550526559353</v>
-      </c>
-      <c r="C10">
-        <v>0.0004515898181125522</v>
-      </c>
-      <c r="D10">
-        <v>2.304499730598764E-06</v>
-      </c>
-      <c r="E10">
-        <v>2.304499730598764E-06</v>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11">
-        <v>0.04133117571473122</v>
-      </c>
-      <c r="C11">
-        <v>0.05791597813367844</v>
-      </c>
-      <c r="D11">
-        <v>0.007795904763042927</v>
-      </c>
-      <c r="E11">
-        <v>0.007795904763042927</v>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -665,16 +665,16 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>7.901372009655461E-05</v>
+        <v>0.0001614262873772532</v>
       </c>
       <c r="C12">
-        <v>0.0003044850018341094</v>
+        <v>0.0003093707491643727</v>
       </c>
       <c r="D12">
-        <v>1.132073430198943E-05</v>
+        <v>1.056747805705527E-05</v>
       </c>
       <c r="E12">
-        <v>1.132073430198943E-05</v>
+        <v>1.056747805705527E-05</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -682,16 +682,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0.0001614262873772532</v>
+        <v>0.01823791675269604</v>
       </c>
       <c r="C13">
-        <v>0.0003093707491643727</v>
+        <v>0.01264662388712168</v>
       </c>
       <c r="D13">
-        <v>1.056747805705527E-05</v>
+        <v>0.001363039249554276</v>
       </c>
       <c r="E13">
-        <v>1.056747805705527E-05</v>
+        <v>0.001363039249554276</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -699,16 +699,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.01803041994571686</v>
+        <v>0.04133117571473122</v>
       </c>
       <c r="C14">
-        <v>0.01235961355268955</v>
+        <v>0.05791597813367844</v>
       </c>
       <c r="D14">
-        <v>0.001358434907160699</v>
+        <v>0.007795904763042927</v>
       </c>
       <c r="E14">
-        <v>0.001358434907160699</v>
+        <v>0.007795904763042927</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -716,16 +716,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>0.02194621413946152</v>
+        <v>7.901372009655461E-05</v>
       </c>
       <c r="C15">
-        <v>0.03095167316496372</v>
+        <v>0.0003044850018341094</v>
       </c>
       <c r="D15">
-        <v>0.00682216277346015</v>
+        <v>1.132073430198943E-05</v>
       </c>
       <c r="E15">
-        <v>0.00682216277346015</v>
+        <v>1.132073430198943E-05</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -733,16 +733,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>0.2837054133415222</v>
+        <v>0.9270660877227783</v>
       </c>
       <c r="C16">
-        <v>0.006657296791672707</v>
+        <v>0.03898121044039726</v>
       </c>
       <c r="D16">
-        <v>2.60684646491427E-05</v>
+        <v>1.319911825703457E-05</v>
       </c>
       <c r="E16">
-        <v>2.60684646491427E-05</v>
+        <v>1.319911825703457E-05</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -750,50 +750,50 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>0.9270660877227783</v>
+        <v>0.01803041994571686</v>
       </c>
       <c r="C17">
-        <v>0.03898121044039726</v>
+        <v>0.01235961355268955</v>
       </c>
       <c r="D17">
-        <v>1.319911825703457E-05</v>
+        <v>0.001358434907160699</v>
       </c>
       <c r="E17">
-        <v>1.319911825703457E-05</v>
+        <v>0.001358434907160699</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" t="s">
-        <v>30</v>
+      <c r="B18">
+        <v>2.120720691379777E-17</v>
+      </c>
+      <c r="C18">
+        <v>2.120720691379777E-17</v>
+      </c>
+      <c r="D18">
+        <v>2.120720691379777E-17</v>
+      </c>
+      <c r="E18">
+        <v>2.120720691379777E-17</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" t="s">
-        <v>31</v>
+      <c r="B19">
+        <v>0.06551679968833923</v>
+      </c>
+      <c r="C19">
+        <v>0.03050441108644009</v>
+      </c>
+      <c r="D19">
+        <v>0.006228530779480934</v>
+      </c>
+      <c r="E19">
+        <v>0.006228530779480934</v>
       </c>
     </row>
   </sheetData>

--- a/MinMax/scripts/comparison/accuracy_comparison_table_118_1000_True.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_118_1000_True.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>Pg Vm Projection True</t>
   </si>
@@ -31,88 +31,94 @@
     <t>Metric [MSE]</t>
   </si>
   <si>
+    <t>pg_tot</t>
+  </si>
+  <si>
+    <t>sample_num</t>
+  </si>
+  <si>
+    <t>pinj_tot</t>
+  </si>
+  <si>
+    <t>qinj_tot</t>
+  </si>
+  <si>
+    <t>vr_tot</t>
+  </si>
+  <si>
+    <t>cost_tot</t>
+  </si>
+  <si>
     <t>Ibr_from_r_tot</t>
   </si>
   <si>
+    <t>Ibr_from_i_tot</t>
+  </si>
+  <si>
+    <t>vi_tot</t>
+  </si>
+  <si>
+    <t>solve_time</t>
+  </si>
+  <si>
+    <t>Iinj_r_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_r_tot</t>
+  </si>
+  <si>
+    <t>qg_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_i_tot</t>
+  </si>
+  <si>
     <t>pd_tot</t>
   </si>
   <si>
+    <t>qd_tot</t>
+  </si>
+  <si>
     <t>slack_tot</t>
   </si>
   <si>
-    <t>pinj_tot</t>
-  </si>
-  <si>
-    <t>qinj_tot</t>
-  </si>
-  <si>
-    <t>vi_tot</t>
-  </si>
-  <si>
-    <t>Iinj_r_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_r_tot</t>
-  </si>
-  <si>
-    <t>solve_time</t>
-  </si>
-  <si>
-    <t>cost_tot</t>
-  </si>
-  <si>
-    <t>vr_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_i_tot</t>
-  </si>
-  <si>
-    <t>qg_tot</t>
+    <t>Iinj_i_tot</t>
   </si>
   <si>
     <t>vm_tot</t>
   </si>
   <si>
-    <t>pg_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_i_tot</t>
-  </si>
-  <si>
-    <t>qd_tot</t>
-  </si>
-  <si>
-    <t>Iinj_i_tot</t>
-  </si>
-  <si>
-    <t>2.45 (1.97)</t>
-  </si>
-  <si>
-    <t>4.77s (20.34 s)</t>
-  </si>
-  <si>
-    <t>89911.75 (70058.73 &gt; 28.66%)</t>
-  </si>
-  <si>
-    <t>1.85 (1.97)</t>
-  </si>
-  <si>
-    <t>3.71s (20.34 s)</t>
-  </si>
-  <si>
-    <t>73759.09 (70058.73 &gt; 5.07%)</t>
-  </si>
-  <si>
-    <t>1.97 (1.97)</t>
-  </si>
-  <si>
-    <t>20.45s (20.34 s)</t>
-  </si>
-  <si>
-    <t>70057.65 (70058.73 &gt; 0.01%)</t>
-  </si>
-  <si>
-    <t>11.78s (20.34 s)</t>
+    <t>89883.75 (70016.30 &gt; 28.38%)</t>
+  </si>
+  <si>
+    <t>0.27s (0.32 s)</t>
+  </si>
+  <si>
+    <t>245.42 (195.05)</t>
+  </si>
+  <si>
+    <t>73746.66 (70072.91 &gt; 5.24%)</t>
+  </si>
+  <si>
+    <t>0.34s (0.32 s)</t>
+  </si>
+  <si>
+    <t>184.34 (197.77)</t>
+  </si>
+  <si>
+    <t>69975.16 (69975.31 &gt; 0.00%)</t>
+  </si>
+  <si>
+    <t>0.33s (0.32 s)</t>
+  </si>
+  <si>
+    <t>195.24 (195.24)</t>
+  </si>
+  <si>
+    <t>70019.85 (70020.01 &gt; 0.00%)</t>
+  </si>
+  <si>
+    <t>195.54 (195.53)</t>
   </si>
 </sst>
 </file>
@@ -470,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -495,50 +501,38 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0.2973946630954742</v>
+        <v>0.947300136089325</v>
       </c>
       <c r="C2">
-        <v>0.007040958385914564</v>
+        <v>0.05629174038767815</v>
       </c>
       <c r="D2">
-        <v>2.632787436596118E-05</v>
+        <v>0.02878091111779213</v>
       </c>
       <c r="E2">
-        <v>2.632787436596118E-05</v>
+        <v>0.02775336243212223</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3">
-        <v>1.415648811724072E-16</v>
-      </c>
-      <c r="C3">
-        <v>1.415648811724072E-16</v>
-      </c>
-      <c r="D3">
-        <v>1.415648811724072E-16</v>
-      </c>
-      <c r="E3">
-        <v>1.415648811724072E-16</v>
-      </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
+      <c r="B4">
+        <v>0.4500132203102112</v>
+      </c>
+      <c r="C4">
+        <v>0.06083493679761887</v>
+      </c>
+      <c r="D4">
+        <v>0.05283879861235619</v>
+      </c>
+      <c r="E4">
+        <v>0.05151749774813652</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -546,16 +540,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>0.4308059215545654</v>
+        <v>0.01895548030734062</v>
       </c>
       <c r="C5">
-        <v>0.02048652805387974</v>
+        <v>0.0248377975076437</v>
       </c>
       <c r="D5">
-        <v>9.185793715005275E-06</v>
+        <v>0.004475073423236609</v>
       </c>
       <c r="E5">
-        <v>9.185793715005275E-06</v>
+        <v>0.004353299736976624</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -563,33 +557,33 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0.02194621413946152</v>
+        <v>0.0004809341626241803</v>
       </c>
       <c r="C6">
-        <v>0.03095167316496372</v>
+        <v>0.0004657224926631898</v>
       </c>
       <c r="D6">
-        <v>0.00682216277346015</v>
+        <v>0.0001937305059982464</v>
       </c>
       <c r="E6">
-        <v>0.00682216277346015</v>
+        <v>0.0001863318175310269</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>0.01917550526559353</v>
-      </c>
-      <c r="C7">
-        <v>0.0004515898181125522</v>
-      </c>
-      <c r="D7">
-        <v>2.304499730598764E-06</v>
-      </c>
-      <c r="E7">
-        <v>2.304499730598764E-06</v>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -597,16 +591,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>0.3592993319034576</v>
+        <v>0.5743690133094788</v>
       </c>
       <c r="C8">
-        <v>0.01769106090068817</v>
+        <v>0.5695143342018127</v>
       </c>
       <c r="D8">
-        <v>9.123721247306094E-05</v>
+        <v>0.5678834319114685</v>
       </c>
       <c r="E8">
-        <v>9.123721247306094E-05</v>
+        <v>0.5684621334075928</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -614,33 +608,33 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>0.2837054133415222</v>
+        <v>0.08649829030036926</v>
       </c>
       <c r="C9">
-        <v>0.006657296791672707</v>
+        <v>0.08646988123655319</v>
       </c>
       <c r="D9">
-        <v>2.60684646491427E-05</v>
+        <v>0.08614364266395569</v>
       </c>
       <c r="E9">
-        <v>2.60684646491427E-05</v>
+        <v>0.08613903075456619</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" t="s">
-        <v>32</v>
+      <c r="B10">
+        <v>0.02001354470849037</v>
+      </c>
+      <c r="C10">
+        <v>0.004760077223181725</v>
+      </c>
+      <c r="D10">
+        <v>0.004866957664489746</v>
+      </c>
+      <c r="E10">
+        <v>0.004758582916110754</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -665,16 +659,16 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.0001614262873772532</v>
+        <v>0.3749898076057434</v>
       </c>
       <c r="C12">
-        <v>0.0003093707491643727</v>
+        <v>0.05807676166296005</v>
       </c>
       <c r="D12">
-        <v>1.056747805705527E-05</v>
+        <v>0.05186183750629425</v>
       </c>
       <c r="E12">
-        <v>1.056747805705527E-05</v>
+        <v>0.05058415234088898</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -682,16 +676,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0.01823791675269604</v>
+        <v>0.5532904267311096</v>
       </c>
       <c r="C13">
-        <v>0.01264662388712168</v>
+        <v>0.5488641858100891</v>
       </c>
       <c r="D13">
-        <v>0.001363039249554276</v>
+        <v>0.5472081303596497</v>
       </c>
       <c r="E13">
-        <v>0.001363039249554276</v>
+        <v>0.5477342009544373</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -699,16 +693,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.04133117571473122</v>
+        <v>0.0365726500749588</v>
       </c>
       <c r="C14">
-        <v>0.05791597813367844</v>
+        <v>0.05165217816829681</v>
       </c>
       <c r="D14">
-        <v>0.007795904763042927</v>
+        <v>0.01116204727441072</v>
       </c>
       <c r="E14">
-        <v>0.007795904763042927</v>
+        <v>0.01086991373449564</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -716,16 +710,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>7.901372009655461E-05</v>
+        <v>0.1002955809235573</v>
       </c>
       <c r="C15">
-        <v>0.0003044850018341094</v>
+        <v>0.09998135268688202</v>
       </c>
       <c r="D15">
-        <v>1.132073430198943E-05</v>
+        <v>0.09976068884134293</v>
       </c>
       <c r="E15">
-        <v>1.132073430198943E-05</v>
+        <v>0.09980523586273193</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -733,16 +727,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>0.9270660877227783</v>
+        <v>0.004506646655499935</v>
       </c>
       <c r="C16">
-        <v>0.03898121044039726</v>
+        <v>0.004727293271571398</v>
       </c>
       <c r="D16">
-        <v>1.319911825703457E-05</v>
+        <v>0.00439748028293252</v>
       </c>
       <c r="E16">
-        <v>1.319911825703457E-05</v>
+        <v>0.004354014992713928</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -750,33 +744,33 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>0.01803041994571686</v>
+        <v>0.0005349938874132931</v>
       </c>
       <c r="C17">
-        <v>0.01235961355268955</v>
+        <v>0.0005694130668416619</v>
       </c>
       <c r="D17">
-        <v>0.001358434907160699</v>
+        <v>0.0005389577709138393</v>
       </c>
       <c r="E17">
-        <v>0.001358434907160699</v>
+        <v>0.0005256885197013617</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B18">
-        <v>2.120720691379777E-17</v>
-      </c>
-      <c r="C18">
-        <v>2.120720691379777E-17</v>
-      </c>
-      <c r="D18">
-        <v>2.120720691379777E-17</v>
-      </c>
-      <c r="E18">
-        <v>2.120720691379777E-17</v>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -784,16 +778,33 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>0.06551679968833923</v>
+        <v>0.06398716568946838</v>
       </c>
       <c r="C19">
-        <v>0.03050441108644009</v>
+        <v>0.02757146395742893</v>
       </c>
       <c r="D19">
-        <v>0.006228530779480934</v>
+        <v>0.00832920428365469</v>
       </c>
       <c r="E19">
-        <v>0.006228530779480934</v>
+        <v>0.008149753324687481</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20">
+        <v>0.0005772572476416826</v>
+      </c>
+      <c r="C20">
+        <v>0.0003102076007053256</v>
+      </c>
+      <c r="D20">
+        <v>1.303653698414564E-05</v>
+      </c>
+      <c r="E20">
+        <v>1.264053480554139E-05</v>
       </c>
     </row>
   </sheetData>
